--- a/output/2026-09-19_23_Croazia_Šibensko-kninska_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-19_23_Croazia_Šibensko-kninska_Componentistica_Ventilazione_industriale.xlsx
@@ -475,7 +475,6 @@
           <t>ADRIA-IMPEX d.o.o.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Šibenik</t>
@@ -498,7 +497,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vendita/installazione ventilazione, climatizzazione, refrigerazione commerciale. Confermata via Kompass, tvrtke.hr, emajstor.hr. Sito originale non più raggiungibile (DNS).</t>
+          <t>Vendita/installazione ventilazione, climatizzazione, refrigerazione commerciale. Confermata via Kompass, tvrtke.hr, emajstor.hr. Sito originale non più raggiungibile (DNS). [DUPLICATO — vedi anche: 2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -540,7 +539,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dealer multimarca (Mitsubishi Electric, Toshiba, Haier). Sito ufficiale attivo, confermato via ricerca web.</t>
+          <t>Dealer multimarca (Mitsubishi Electric, Toshiba, Haier). Sito ufficiale attivo, confermato via ricerca web. [DUPLICATO — vedi anche: 2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -582,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dealer ufficiale Daikin (confermato nel dealer locator ufficiale daikin.hr), Mitsubishi Electric, Toshiba, Panasonic, Gree.</t>
+          <t>Dealer ufficiale Daikin (confermato nel dealer locator ufficiale daikin.hr), Mitsubishi Electric, Toshiba, Panasonic, Gree. [DUPLICATO — vedi anche: 2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -597,7 +596,6 @@
           <t>ELEKTROLUX GRAĐENJE d.o.o.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Šibenik</t>
@@ -620,7 +618,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Commercio condizionatori/ventilazione. Confermata via fininfo.hr/companywall.hr (direttore Nikica Bujas). Non confondere con altre entità omonime.</t>
+          <t>Commercio condizionatori/ventilazione. Confermata via fininfo.hr/companywall.hr (direttore Nikica Bujas). Non confondere con altre entità omonime. [DUPLICATO — vedi anche: 2026-09-19_21_Croazia_Sibensko-kninska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -704,7 +702,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dealer ufficiale Weishaupt, centro autorizzato Ariston. Confermata via sito ufficiale ed energetika-net.com.</t>
+          <t>Dealer ufficiale Weishaupt, centro autorizzato Ariston. Confermata via sito ufficiale ed energetika-net.com. [DUPLICATO — vedi anche: 2026-09-19_22_Croazia_Sibensko-kninska_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
